--- a/excel/Users.xlsx
+++ b/excel/Users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paraj\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{166280AC-54C8-4689-8D67-8B55E28DF22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{381A11AD-4B1B-4556-8E73-61D64727794A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1DB1981-AA59-439A-AD6A-AC1893567FBD}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D1DB1981-AA59-439A-AD6A-AC1893567FBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>FirstName</t>
   </si>
@@ -53,28 +53,34 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Pérez</t>
-  </si>
-  <si>
     <t>Pass123!</t>
   </si>
   <si>
-    <t>Ana</t>
-  </si>
-  <si>
-    <t>Gómez</t>
-  </si>
-  <si>
-    <t>ana@email.com</t>
-  </si>
-  <si>
     <t>AnaPass!</t>
   </si>
   <si>
-    <t>jsdsdsdn@email.com</t>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>Valencia</t>
+  </si>
+  <si>
+    <t>Valencia@email.com</t>
+  </si>
+  <si>
+    <t>Camilo</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>balanta</t>
+  </si>
+  <si>
+    <t>lopez</t>
+  </si>
+  <si>
+    <t>camilo@email.com</t>
   </si>
 </sst>
 </file>
@@ -127,7 +133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,6 +144,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -473,8 +480,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6FD1020-8813-456B-9EBA-F4D27B2B20E9}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -493,43 +503,62 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
         <v>3001234567</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="2">
         <v>3117654321</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>3118372789</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{807300B3-A589-49A6-A32C-04930811DF5C}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{F82B28EF-C495-4007-98A2-3FDBCC22FE11}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{C93A77A0-408C-4A74-86C4-7960F139753A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/Users.xlsx
+++ b/excel/Users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paraj\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{381A11AD-4B1B-4556-8E73-61D64727794A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAEEF7F5-67A5-4A6B-9C43-303B8E9F0CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D1DB1981-AA59-439A-AD6A-AC1893567FBD}"/>
   </bookViews>
@@ -80,7 +80,7 @@
     <t>lopez</t>
   </si>
   <si>
-    <t>camilo@email.com</t>
+    <t>camil1o@email.com</t>
   </si>
 </sst>
 </file>
